--- a/discharge_forms/030_hiv_aids_discharge_form--discharge_forms.xlsx
+++ b/discharge_forms/030_hiv_aids_discharge_form--discharge_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1279,17 +1279,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>follow_up_contact_choices</t>
+          <t>discharge_reason_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>jane</t>
+          <t>discharge_for_medical_reasons</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Discharge for Medical Reasons</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>discharge_for_medical_reasons</t>
+          <t>discharge_for_non_medical_reasons</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Discharge for Medical Reasons</t>
+          <t>Discharge for Non Medical Reasons</t>
         </is>
       </c>
     </row>
@@ -1318,27 +1318,10 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>discharge_for_non_medical_reasons</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>Discharge for Non Medical Reasons</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>discharge_reason_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
